--- a/data/trans_orig/IP31KM07_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM07_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27628</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33965</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42465</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38098</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44763</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>35204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41027</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84527</t>
+          <t>74090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3470</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9807</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8397</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>139802</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>131336</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145364</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>144904</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>138069</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>150055</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161682</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>124493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168838</t>
+          <t>136442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>306586</t>
+          <t>271718</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>261655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>315872</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17240</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11678</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25706</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14395</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9244</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21230</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29585</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>40905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>178736</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>169557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>186114</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>153045</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>140716</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>160525</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>190628</t>
+          <t>156857</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180272</t>
+          <t>149000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198520</t>
+          <t>163565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>343675</t>
+          <t>335592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>328536</t>
+          <t>323211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354802</t>
+          <t>345879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21390</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14012</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30569</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20027</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12547</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32356</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57027</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>253652</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>235824</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>265568</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>226416</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>160190</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>253149</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>257745</t>
+          <t>231053</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236285</t>
+          <t>218490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274749</t>
+          <t>238819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>484161</t>
+          <t>484705</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>400781</t>
+          <t>462180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>516764</t>
+          <t>499206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38569</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26653</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56397</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>47851</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21118</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>114077</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>95105</t>
+          <t>62853</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62502</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178485</t>
+          <t>85378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>582763</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>619772</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>830</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>566831</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>481405</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>596171</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623159</t>
+          <t>544874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667911</t>
+          <t>570790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1129051</t>
+          <t>1137367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1246222</t>
+          <t>1185217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>83472</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>86303</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56963</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>171729</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>183066</t>
+          <t>142735</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151645</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268816</t>
+          <t>167664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
